--- a/dataset/construct/dataset_splits/data_size/5_percent/merged/fold3.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/merged/fold3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2642</v>
+        <v>611</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,79 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>78.0542406266636</v>
+        <v>86.12057761046469</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>25.390625</v>
       </c>
       <c r="E2" t="n">
-        <v>26.5021162137573</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>59</v>
+        <v>431</v>
       </c>
       <c r="I2" t="n">
-        <v>1460</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>476</v>
+        <v>50</v>
       </c>
       <c r="M2" t="n">
-        <v>477</v>
+        <v>33</v>
       </c>
       <c r="N2" t="n">
-        <v>1276</v>
+        <v>64</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X2" t="n">
-        <v>24.15</v>
+        <v>22.5639660829322</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.256317689530686</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.3188184364655</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>23.866127828619</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -730,33 +715,22 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>128</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>191</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1265</v>
+        <v>2601</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -764,85 +738,85 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>52.5566858379598</v>
+        <v>80.6226186402008</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>34.2403214024835</v>
       </c>
       <c r="E3" t="n">
-        <v>20.0065693212696</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>46</v>
+        <v>377</v>
       </c>
       <c r="I3" t="n">
-        <v>4500</v>
+        <v>83</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="K3" t="n">
-        <v>328</v>
+        <v>543</v>
       </c>
       <c r="L3" t="n">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="M3" t="n">
-        <v>345</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>915</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="Q3" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>136</v>
+        <v>23.15</v>
       </c>
       <c r="V3" t="n">
-        <v>335</v>
+        <v>0.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>23.1410746116628</v>
       </c>
       <c r="X3" t="n">
-        <v>25.45</v>
+        <v>22.7940734179357</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.162454873646209</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>25.2524956816771</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -862,25 +836,12 @@
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>132</v>
-      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54050556</v>
+        <v>51991959</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -888,79 +849,91 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.17659137577</v>
+        <v>78.52429842573579</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>22.65625</v>
       </c>
       <c r="E4" t="n">
-        <v>22.265625</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>55</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>416</v>
+      </c>
+      <c r="I4" t="n">
+        <v>329</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>530</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L4" t="n">
+        <v>416</v>
+      </c>
+      <c r="M4" t="n">
+        <v>302</v>
+      </c>
+      <c r="N4" t="n">
+        <v>503</v>
+      </c>
       <c r="O4" t="n">
-        <v>152</v>
+        <v>1221</v>
       </c>
       <c r="P4" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>524</v>
+        <v>63</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V4" t="n">
-        <v>32</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>27.94760800693682</v>
       </c>
       <c r="X4" t="n">
-        <v>21.9</v>
+        <v>26.85684646589152</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>72.3</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>385.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -969,30 +942,21 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>51951854</v>
+        <v>52234455</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1000,83 +964,85 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81.968514715948</v>
+        <v>85.9739904175222</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>29.3333333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>27.7551020408163</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>45</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>259</v>
+      </c>
+      <c r="I5" t="n">
+        <v>204</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="K5" t="n">
-        <v>367</v>
+        <v>633</v>
       </c>
       <c r="L5" t="n">
-        <v>350</v>
+        <v>233</v>
       </c>
       <c r="M5" t="n">
-        <v>451</v>
+        <v>146</v>
       </c>
       <c r="N5" t="n">
-        <v>1168</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
-        <v>260</v>
+        <v>508</v>
       </c>
       <c r="P5" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>275</v>
+        <v>39</v>
       </c>
       <c r="R5" t="n">
-        <v>813</v>
+        <v>258</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>25.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>25.49662188332163</v>
       </c>
       <c r="X5" t="n">
-        <v>27.3</v>
+        <v>24.87301941435369</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>89.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>595.3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1085,32 +1051,27 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>165</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>52772610</v>
+        <v>54213221</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1118,73 +1079,71 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.2313483915127</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>75.98083504449011</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.4055043555107</v>
+      </c>
       <c r="E6" t="n">
-        <v>24.3417582863402</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>622</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>632</v>
+        <v>368</v>
       </c>
       <c r="M6" t="n">
-        <v>653</v>
+        <v>376</v>
       </c>
       <c r="N6" t="n">
-        <v>1907</v>
+        <v>238</v>
       </c>
       <c r="O6" t="n">
-        <v>622</v>
+        <v>982</v>
       </c>
       <c r="P6" t="n">
-        <v>431</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="n">
-        <v>622</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1675</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>88</v>
+        <v>27.7</v>
       </c>
       <c r="V6" t="n">
-        <v>88</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>28.20225591588385</v>
       </c>
       <c r="X6" t="n">
-        <v>31.1</v>
+        <v>27.75216389059239</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>101.6</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1193,38 +1152,33 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54382225</v>
+        <v>51817571</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1232,71 +1186,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79.00889801505819</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>88.5694729637235</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28.6214703746422</v>
+      </c>
       <c r="E7" t="n">
-        <v>25.7629805786762</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57</v>
+      </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>66</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="I7" t="n">
+        <v>198</v>
+      </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="K7" t="n">
+        <v>482</v>
+      </c>
+      <c r="L7" t="n">
+        <v>182</v>
+      </c>
+      <c r="M7" t="n">
+        <v>57</v>
+      </c>
+      <c r="N7" t="n">
+        <v>62</v>
+      </c>
       <c r="O7" t="n">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="P7" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1168</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>22.7</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>22.6636638962859</v>
       </c>
       <c r="X7" t="n">
-        <v>25.5</v>
+        <v>21.88881085586519</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.14</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>508.9</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1308,33 +1276,20 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>127</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>114</v>
-      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>55148478</v>
+        <v>51673055</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1342,74 +1297,88 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>82.072553045859</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>79.74264202600961</v>
+      </c>
+      <c r="D8" t="n">
+        <v>20.9643605870021</v>
+      </c>
       <c r="E8" t="n">
-        <v>34.8087496538903</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>45</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>49</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="I8" t="n">
+        <v>87</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>115</v>
+      </c>
+      <c r="K8" t="n">
+        <v>237</v>
+      </c>
+      <c r="L8" t="n">
+        <v>35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>81</v>
+      </c>
+      <c r="N8" t="n">
+        <v>115</v>
+      </c>
       <c r="O8" t="n">
-        <v>122</v>
+        <v>231</v>
       </c>
       <c r="P8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="R8" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>26.32422758739949</v>
       </c>
       <c r="X8" t="n">
-        <v>23.4</v>
+        <v>24.61315451917918</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>453.9</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1421,30 +1390,17 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>126</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54908834</v>
+        <v>52996171</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1452,65 +1408,71 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82.2231348391513</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>84.7227926078029</v>
+      </c>
+      <c r="D9" t="n">
+        <v>26.0261748958953</v>
+      </c>
       <c r="E9" t="n">
-        <v>29.7619047619048</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>55</v>
+      </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>55</v>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>128.14604</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.238129000000001</v>
+      </c>
+      <c r="N9" t="n">
+        <v>25.206894</v>
+      </c>
       <c r="O9" t="n">
-        <v>482</v>
+        <v>162.591063</v>
       </c>
       <c r="P9" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>726</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1709</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>130</v>
+        <v>20.387993</v>
       </c>
       <c r="V9" t="n">
-        <v>137</v>
+        <v>0.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>21.7351444089912</v>
       </c>
       <c r="X9" t="n">
-        <v>30.1</v>
+        <v>21.03475523299063</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>99.3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>660.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1519,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1531,26 +1493,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>150</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
